--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N75_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N75_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.8191375710338</v>
+        <v>3.708109855292993</v>
       </c>
       <c r="D2" t="n">
-        <v>30.61207936619351</v>
+        <v>4.974462897006445</v>
       </c>
       <c r="E2" t="n">
-        <v>5.938071907022128</v>
+        <v>0.9649366848910959</v>
       </c>
       <c r="F2" t="n">
-        <v>16.15193848296111</v>
+        <v>2.62469000348118</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.05394573528271</v>
+        <v>2.121266181983441</v>
       </c>
       <c r="D3" t="n">
-        <v>12.94971021300775</v>
+        <v>2.104327909613759</v>
       </c>
       <c r="E3" t="n">
-        <v>5.938071907022128</v>
+        <v>0.9649366848910959</v>
       </c>
       <c r="F3" t="n">
-        <v>16.15193848296111</v>
+        <v>2.62469000348118</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.79016098274876</v>
+        <v>3.703401159696673</v>
       </c>
       <c r="D4" t="n">
-        <v>57.67561911075708</v>
+        <v>9.372288105498026</v>
       </c>
       <c r="E4" t="n">
-        <v>5.938071907022128</v>
+        <v>0.9649366848910959</v>
       </c>
       <c r="F4" t="n">
-        <v>16.15193848296111</v>
+        <v>2.62469000348118</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>9.617692030835672</v>
+        <v>1.562874955010797</v>
       </c>
       <c r="D5" t="n">
-        <v>18.04007883697974</v>
+        <v>2.931512811009208</v>
       </c>
       <c r="E5" t="n">
-        <v>5.938071907022128</v>
+        <v>0.9649366848910959</v>
       </c>
       <c r="F5" t="n">
-        <v>16.15193848296111</v>
+        <v>2.62469000348118</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.20037878244409</v>
+        <v>2.145061552147164</v>
       </c>
       <c r="D6" t="n">
-        <v>12.96028932072088</v>
+        <v>2.106047014617143</v>
       </c>
       <c r="E6" t="n">
-        <v>5.938071907022128</v>
+        <v>0.9649366848910959</v>
       </c>
       <c r="F6" t="n">
-        <v>16.15193848296111</v>
+        <v>2.62469000348118</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>5.70087712549569</v>
+        <v>0.9263925328930496</v>
       </c>
       <c r="D7" t="n">
-        <v>5.559802781493184</v>
+        <v>0.9034679519926425</v>
       </c>
       <c r="E7" t="n">
-        <v>5.938071907022128</v>
+        <v>0.9649366848910959</v>
       </c>
       <c r="F7" t="n">
-        <v>16.15193848296111</v>
+        <v>2.62469000348118</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>16.65082580534671</v>
+        <v>2.705759193368841</v>
       </c>
       <c r="D8" t="n">
-        <v>16.54930076127231</v>
+        <v>2.68926137370675</v>
       </c>
       <c r="E8" t="n">
-        <v>5.938071907022128</v>
+        <v>0.9649366848910959</v>
       </c>
       <c r="F8" t="n">
-        <v>16.15193848296111</v>
+        <v>2.62469000348118</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
